--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484148_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484148_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.548</v>
+        <v>3.1769</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6642</v>
+        <v>0.9103</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8838</v>
+        <v>2.2665</v>
       </c>
       <c r="G2" t="n">
         <v>2.657</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1731</v>
+        <v>0.802</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9297</v>
+        <v>0.1758</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2434</v>
+        <v>0.6262</v>
       </c>
       <c r="V2" t="n">
         <v>-1.4724</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9368</v>
+        <v>1.6318</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0446</v>
+        <v>3.2907</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1078</v>
+        <v>-1.6589</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9026</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1407</v>
+        <v>-0.1643</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0034</v>
+        <v>0.2495</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8627</v>
+        <v>-0.4139</v>
       </c>
       <c r="V3" t="n">
         <v>3.6907</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.234</v>
+        <v>1.6086</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9012</v>
+        <v>1.332</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3328</v>
+        <v>0.2767</v>
       </c>
       <c r="G4" t="n">
         <v>3.4925</v>
@@ -766,13 +766,13 @@
         <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0601</v>
+        <v>0.3146</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2946</v>
+        <v>0.1361</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2345</v>
+        <v>0.1784</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2065</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0893</v>
+        <v>1.2395</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3997</v>
+        <v>1.8304</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3104</v>
+        <v>-0.5909</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1597</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0964</v>
+        <v>0.0538</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2946</v>
+        <v>0.1361</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1982</v>
+        <v>-0.0823</v>
       </c>
       <c r="V5" t="n">
         <v>1.5437</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2093</v>
+        <v>-0.8078</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3342</v>
+        <v>-1.3536</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1249</v>
+        <v>0.5457</v>
       </c>
       <c r="G6" t="n">
         <v>-2.3089</v>
@@ -922,13 +922,13 @@
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6182</v>
+        <v>-0.2168</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1732</v>
+        <v>-0.1926</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.445</v>
+        <v>-0.0242</v>
       </c>
       <c r="V6" t="n">
         <v>-0.266</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6137</v>
+        <v>-3.0091</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3579</v>
+        <v>-3.8721</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2558</v>
+        <v>0.8631</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3733</v>
+        <v>-2.8347</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5675</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8058</v>
+        <v>-2.1195</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1766</v>
+        <v>-2.9475</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2971</v>
+        <v>-1.0675</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>-1.8799</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1967</v>
+        <v>0.1127</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2704</v>
+        <v>0.3523</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9263</v>
+        <v>-0.2396</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4223</v>
+        <v>0.0241</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8106</v>
+        <v>-0.4647</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3883</v>
+        <v>0.4888</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.266</v>
+        <v>-0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6198</v>
+        <v>-3.2273</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3426</v>
+        <v>-1.1118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7228</v>
+        <v>-2.1155</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8347</v>
+        <v>-2.3733</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-1.5675</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1195</v>
+        <v>-0.8058</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.9475</v>
+        <v>-0.1766</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0675</v>
+        <v>-0.2971</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8799</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1127</v>
+        <v>-2.1967</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3523</v>
+        <v>-1.2704</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2396</v>
+        <v>-0.9263</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5867</v>
+        <v>-0.1913</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9352</v>
+        <v>0.0567</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3485</v>
+        <v>-0.248</v>
       </c>
       <c r="V8" t="n">
-        <v>-0</v>
+        <v>-0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.532</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6465</v>
+        <v>-3.3623</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8533</v>
+        <v>-2.4849</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7932</v>
+        <v>-0.8774</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8969</v>
@@ -1156,13 +1156,13 @@
         <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4756</v>
+        <v>-0.1913</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7991</v>
+        <v>-0.4307</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3236</v>
+        <v>0.2394</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4724</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7616</v>
+        <v>-4.6698</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9675</v>
+        <v>-4.7634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2058</v>
+        <v>0.0936</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3454</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4126</v>
+        <v>0.5044</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4364</v>
+        <v>-0.2324</v>
       </c>
       <c r="U10" t="n">
-        <v>0.849</v>
+        <v>0.7368</v>
       </c>
       <c r="V10" t="n">
         <v>-0.266</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.042800000000002</v>
+        <v>-7.419499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8458</v>
+        <v>-6.222399999999999</v>
       </c>
       <c r="F11" t="n">
         <v>-1.1971</v>
@@ -1285,10 +1285,10 @@
         <v>-4.5989</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6418</v>
+        <v>4.641800000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4686</v>
+        <v>1.468600000000001</v>
       </c>
       <c r="L11" t="n">
         <v>3.173499999999999</v>
@@ -1312,10 +1312,10 @@
         <v>12.8949</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3116999999999998</v>
+        <v>0.9352</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1894</v>
+        <v>-0.5661999999999998</v>
       </c>
       <c r="U11" t="n">
         <v>1.5012</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.0102</v>
+        <v>5.3225</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8297</v>
+        <v>3.6939</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1805</v>
+        <v>1.6286</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5124</v>
+        <v>2.5784</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3905</v>
+        <v>2.0563</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1219</v>
+        <v>0.5221</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6571</v>
+        <v>2.8607</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2956</v>
+        <v>2.0925</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3615</v>
+        <v>0.7682</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1447</v>
+        <v>-0.2823</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0949</v>
+        <v>-0.0363</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2396</v>
+        <v>-0.2461</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R12" t="n">
         <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7755</v>
+        <v>0.5413</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4262</v>
+        <v>-0.0566</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3494</v>
+        <v>0.5979</v>
       </c>
       <c r="V12" t="n">
-        <v>0.532</v>
+        <v>2.0044</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7384</v>
+        <v>2.8736</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2065</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1882</v>
+        <v>4.8685</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3.1973</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1881</v>
+        <v>1.6712</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5784</v>
+        <v>1.5124</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0563</v>
+        <v>1.3905</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5221</v>
+        <v>0.1219</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8607</v>
+        <v>1.6571</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0925</v>
+        <v>1.2956</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7682</v>
+        <v>0.3615</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2823</v>
+        <v>-0.1447</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0363</v>
+        <v>0.0949</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2461</v>
+        <v>-0.2396</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>0.407</v>
+        <v>1.6338</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2495</v>
+        <v>0.7937</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1575</v>
+        <v>0.8401</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0044</v>
+        <v>0.532</v>
       </c>
       <c r="W13" t="n">
-        <v>2.8736</v>
+        <v>1.7384</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8692</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3738</v>
+        <v>2.965</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6172</v>
+        <v>1.092</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7566000000000001</v>
+        <v>1.8731</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3011</v>
+        <v>2.6192</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5348000000000001</v>
+        <v>1.4107</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8359</v>
+        <v>1.2086</v>
       </c>
       <c r="J14" t="n">
-        <v>3.216</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
-        <v>0.121</v>
+        <v>1.3158</v>
       </c>
       <c r="L14" t="n">
-        <v>3.095</v>
+        <v>1.5842</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.2807</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6558</v>
+        <v>0.0949</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2591</v>
+        <v>-0.3756</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9868</v>
+        <v>0.3458</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8728</v>
+        <v>0.1758</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.114</v>
+        <v>0.1699</v>
       </c>
       <c r="V14" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1938</v>
+        <v>2.6961</v>
       </c>
       <c r="E15" t="n">
-        <v>2.39</v>
+        <v>1.7192</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1961</v>
+        <v>0.9768</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2087</v>
+        <v>2.3011</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0556</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1531</v>
+        <v>2.8359</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2401</v>
+        <v>3.216</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1656</v>
+        <v>0.121</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4057</v>
+        <v>3.095</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0314</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2212</v>
+        <v>-0.6558</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2526</v>
+        <v>-0.2591</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7408</v>
+        <v>-0.6646</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0566</v>
+        <v>-0.7708</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6842</v>
+        <v>0.1062</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3373</v>
+        <v>0.266</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.972</v>
+        <v>2.5365</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6838</v>
+        <v>2.2879</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2881</v>
+        <v>0.2485</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6192</v>
+        <v>1.2087</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4107</v>
+        <v>0.0556</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2086</v>
+        <v>1.1531</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9</v>
+        <v>1.2401</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3158</v>
+        <v>-0.1656</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5842</v>
+        <v>1.4057</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2807</v>
+        <v>-0.0314</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0949</v>
+        <v>0.2212</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3756</v>
+        <v>-0.2526</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6473</v>
+        <v>-0.3982</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2323</v>
+        <v>-0.1586</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.415</v>
+        <v>-0.2395</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0888</v>
+        <v>0.8558</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1171</v>
+        <v>-0.5049</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0283</v>
+        <v>1.3607</v>
       </c>
       <c r="G17" t="n">
         <v>0.041</v>
@@ -1780,13 +1780,13 @@
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.725</v>
+        <v>0.2196</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8615</v>
+        <v>-0.2493</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1365</v>
+        <v>0.469</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9683</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9615</v>
+        <v>-0.3966</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9932</v>
+        <v>-0.5173</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.616</v>
+        <v>-0.9487</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2313</v>
+        <v>-2.5953</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8473000000000001</v>
+        <v>1.6466</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1862</v>
+        <v>-0.1076</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4085</v>
+        <v>-2.0003</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5948</v>
+        <v>1.8927</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4298</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1772</v>
+        <v>-0.5951</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2526</v>
+        <v>-0.2461</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8417</v>
+        <v>-0.5441</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0057</v>
+        <v>-0.289</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8359</v>
+        <v>-0.2551</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1947</v>
+        <v>-1.2065</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5362</v>
+        <v>-1.2191</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9067</v>
+        <v>-3.0636</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6294999999999999</v>
+        <v>1.8445</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9487</v>
+        <v>-0.616</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5953</v>
+        <v>0.2313</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6466</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1076</v>
+        <v>-0.1862</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.0003</v>
+        <v>0.4085</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8927</v>
+        <v>-0.5948</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.4298</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5951</v>
+        <v>-0.1772</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2461</v>
+        <v>-0.2526</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7855</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1665</v>
+        <v>0.5909</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7991</v>
+        <v>-0.0963</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3673</v>
+        <v>0.6872</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2065</v>
+        <v>0.1947</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8923</v>
+        <v>-2.6244</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0685</v>
+        <v>-3.6604</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1762</v>
+        <v>1.0359</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6481</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4506</v>
+        <v>-0.1828</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6744</v>
+        <v>-0.2663</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2238</v>
+        <v>0.0835</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2094</v>
+        <v>-5.0836</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2699</v>
+        <v>-3.1679</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9395</v>
+        <v>-1.9157</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3759</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.619</v>
+        <v>-0.4931</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6858</v>
+        <v>-0.5838</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0668</v>
+        <v>0.0906</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4129</v>
@@ -2125,34 +2125,34 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>8.042999999999996</v>
+        <v>9.403500000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.196999999999999</v>
+        <v>1.196900000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>6.845899999999999</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="G22" t="n">
         <v>4.6721</v>
       </c>
       <c r="H22" t="n">
-        <v>0.07329999999999981</v>
+        <v>0.07329999999999959</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5989</v>
+        <v>4.598900000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>9.314</v>
+        <v>9.314000000000002</v>
       </c>
       <c r="K22" t="n">
         <v>1.541599999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>7.772399999999999</v>
+        <v>7.772399999999998</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.641799999999999</v>
+        <v>-4.6418</v>
       </c>
       <c r="N22" t="n">
         <v>-1.4685</v>
@@ -2170,13 +2170,13 @@
         <v>16.8627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3118</v>
+        <v>1.0486</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5011</v>
+        <v>-1.5012</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1894</v>
+        <v>2.5498</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2849999999999997</v>
